--- a/docs/client-report/reports/SALES_REPORT_ALL_TIME.xlsx
+++ b/docs/client-report/reports/SALES_REPORT_ALL_TIME.xlsx
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <f>355.98+SUM('AMAZON'!$V$9:$V$208)</f>
+        <f>356.98+SUM('AMAZON'!$V$9:$V$208)</f>
       </c>
       <c r="G6" s="4">
         <v>54</v>
@@ -1124,7 +1124,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <f>98.57+SUM('EBAY'!$Y$5:$Y$204)</f>
+        <f>99.57+SUM('EBAY'!$Y$5:$Y$204)</f>
       </c>
       <c r="G8" s="4">
         <v>19.2</v>
@@ -2072,7 +2072,7 @@
         <f>R3*20%</f>
       </c>
       <c r="T3" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="13">
         <f>O3+Q3+S3</f>
@@ -2167,7 +2167,7 @@
         <f>R4*20%</f>
       </c>
       <c r="T4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" s="4">
         <f>O4+Q4+S4</f>
@@ -19566,7 +19566,7 @@
         <f>U2*20%</f>
       </c>
       <c r="W2" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" s="4">
         <f>Q2+T2+V2</f>
@@ -46420,10 +46420,10 @@
         <v>9.99</v>
       </c>
       <c r="J2" s="13">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="K2" s="17">
-        <v>25.07</v>
+        <v>56.32</v>
       </c>
       <c r="L2" s="11" t="s">
         <v>1</v>
@@ -46458,10 +46458,10 @@
         <v>17.97</v>
       </c>
       <c r="J3" s="4">
-        <v>6.83</v>
+        <v>7.83</v>
       </c>
       <c r="K3" s="18">
-        <v>38.01</v>
+        <v>43.57</v>
       </c>
       <c r="L3" t="s">
         <v>1</v>
@@ -46496,10 +46496,10 @@
         <v>39.96</v>
       </c>
       <c r="J4" s="4">
-        <v>15.21</v>
+        <v>16.21</v>
       </c>
       <c r="K4" s="18">
-        <v>118.82</v>
+        <v>126.63</v>
       </c>
       <c r="L4" t="s">
         <v>1</v>

--- a/docs/client-report/reports/SALES_REPORT_ALL_TIME.xlsx
+++ b/docs/client-report/reports/SALES_REPORT_ALL_TIME.xlsx
@@ -19575,7 +19575,7 @@
         <f>L2-M2-R2-S2-T2-U2-V2-W2</f>
       </c>
       <c r="Z2" s="4">
-        <f>(Y2-AB2)/K2*100</f>
+        <f>(Y2-AB2)/J2*100</f>
       </c>
       <c r="AA2" s="4">
         <f>M2-X2</f>
@@ -19664,7 +19664,7 @@
         <f>L3-M3-R3-S3-T3-U3-V3-W3</f>
       </c>
       <c r="Z3" s="4">
-        <f>(Y3-AB3)/K3*100</f>
+        <f>(Y3-AB3)/J3*100</f>
       </c>
       <c r="AA3" s="4">
         <f>M3-X3</f>
@@ -19753,7 +19753,7 @@
         <f>L4-M4-R4-S4-T4-U4-V4-W4</f>
       </c>
       <c r="Z4" s="13">
-        <f>(Y4-AB4)/K4*100</f>
+        <f>(Y4-AB4)/J4*100</f>
       </c>
       <c r="AA4" s="13">
         <f>M4-X4</f>
@@ -19822,7 +19822,7 @@
         <f>IF($K5="","",L5-M5-R5-S5-T5-U5-V5-W5)</f>
       </c>
       <c r="Z5" s="4">
-        <f>IF($K5="","",(Y5-AB5)/K5*100)</f>
+        <f>IF($K5="","",(Y5-AB5)/J5*100)</f>
       </c>
       <c r="AA5" s="4">
         <f>IF($K5="","",M5-X5)</f>
@@ -19873,7 +19873,7 @@
         <f>IF($K6="","",L6-M6-R6-S6-T6-U6-V6-W6)</f>
       </c>
       <c r="Z6" s="4">
-        <f>IF($K6="","",(Y6-AB6)/K6*100)</f>
+        <f>IF($K6="","",(Y6-AB6)/J6*100)</f>
       </c>
       <c r="AA6" s="4">
         <f>IF($K6="","",M6-X6)</f>
@@ -19924,7 +19924,7 @@
         <f>IF($K7="","",L7-M7-R7-S7-T7-U7-V7-W7)</f>
       </c>
       <c r="Z7" s="4">
-        <f>IF($K7="","",(Y7-AB7)/K7*100)</f>
+        <f>IF($K7="","",(Y7-AB7)/J7*100)</f>
       </c>
       <c r="AA7" s="4">
         <f>IF($K7="","",M7-X7)</f>
@@ -19975,7 +19975,7 @@
         <f>IF($K8="","",L8-M8-R8-S8-T8-U8-V8-W8)</f>
       </c>
       <c r="Z8" s="4">
-        <f>IF($K8="","",(Y8-AB8)/K8*100)</f>
+        <f>IF($K8="","",(Y8-AB8)/J8*100)</f>
       </c>
       <c r="AA8" s="4">
         <f>IF($K8="","",M8-X8)</f>
@@ -20026,7 +20026,7 @@
         <f>IF($K9="","",L9-M9-R9-S9-T9-U9-V9-W9)</f>
       </c>
       <c r="Z9" s="4">
-        <f>IF($K9="","",(Y9-AB9)/K9*100)</f>
+        <f>IF($K9="","",(Y9-AB9)/J9*100)</f>
       </c>
       <c r="AA9" s="4">
         <f>IF($K9="","",M9-X9)</f>
@@ -20077,7 +20077,7 @@
         <f>IF($K10="","",L10-M10-R10-S10-T10-U10-V10-W10)</f>
       </c>
       <c r="Z10" s="4">
-        <f>IF($K10="","",(Y10-AB10)/K10*100)</f>
+        <f>IF($K10="","",(Y10-AB10)/J10*100)</f>
       </c>
       <c r="AA10" s="4">
         <f>IF($K10="","",M10-X10)</f>
@@ -20128,7 +20128,7 @@
         <f>IF($K11="","",L11-M11-R11-S11-T11-U11-V11-W11)</f>
       </c>
       <c r="Z11" s="4">
-        <f>IF($K11="","",(Y11-AB11)/K11*100)</f>
+        <f>IF($K11="","",(Y11-AB11)/J11*100)</f>
       </c>
       <c r="AA11" s="4">
         <f>IF($K11="","",M11-X11)</f>
@@ -20179,7 +20179,7 @@
         <f>IF($K12="","",L12-M12-R12-S12-T12-U12-V12-W12)</f>
       </c>
       <c r="Z12" s="4">
-        <f>IF($K12="","",(Y12-AB12)/K12*100)</f>
+        <f>IF($K12="","",(Y12-AB12)/J12*100)</f>
       </c>
       <c r="AA12" s="4">
         <f>IF($K12="","",M12-X12)</f>
@@ -20230,7 +20230,7 @@
         <f>IF($K13="","",L13-M13-R13-S13-T13-U13-V13-W13)</f>
       </c>
       <c r="Z13" s="4">
-        <f>IF($K13="","",(Y13-AB13)/K13*100)</f>
+        <f>IF($K13="","",(Y13-AB13)/J13*100)</f>
       </c>
       <c r="AA13" s="4">
         <f>IF($K13="","",M13-X13)</f>
@@ -20281,7 +20281,7 @@
         <f>IF($K14="","",L14-M14-R14-S14-T14-U14-V14-W14)</f>
       </c>
       <c r="Z14" s="4">
-        <f>IF($K14="","",(Y14-AB14)/K14*100)</f>
+        <f>IF($K14="","",(Y14-AB14)/J14*100)</f>
       </c>
       <c r="AA14" s="4">
         <f>IF($K14="","",M14-X14)</f>
@@ -20332,7 +20332,7 @@
         <f>IF($K15="","",L15-M15-R15-S15-T15-U15-V15-W15)</f>
       </c>
       <c r="Z15" s="4">
-        <f>IF($K15="","",(Y15-AB15)/K15*100)</f>
+        <f>IF($K15="","",(Y15-AB15)/J15*100)</f>
       </c>
       <c r="AA15" s="4">
         <f>IF($K15="","",M15-X15)</f>
@@ -20383,7 +20383,7 @@
         <f>IF($K16="","",L16-M16-R16-S16-T16-U16-V16-W16)</f>
       </c>
       <c r="Z16" s="4">
-        <f>IF($K16="","",(Y16-AB16)/K16*100)</f>
+        <f>IF($K16="","",(Y16-AB16)/J16*100)</f>
       </c>
       <c r="AA16" s="4">
         <f>IF($K16="","",M16-X16)</f>
@@ -20434,7 +20434,7 @@
         <f>IF($K17="","",L17-M17-R17-S17-T17-U17-V17-W17)</f>
       </c>
       <c r="Z17" s="4">
-        <f>IF($K17="","",(Y17-AB17)/K17*100)</f>
+        <f>IF($K17="","",(Y17-AB17)/J17*100)</f>
       </c>
       <c r="AA17" s="4">
         <f>IF($K17="","",M17-X17)</f>
@@ -20485,7 +20485,7 @@
         <f>IF($K18="","",L18-M18-R18-S18-T18-U18-V18-W18)</f>
       </c>
       <c r="Z18" s="4">
-        <f>IF($K18="","",(Y18-AB18)/K18*100)</f>
+        <f>IF($K18="","",(Y18-AB18)/J18*100)</f>
       </c>
       <c r="AA18" s="4">
         <f>IF($K18="","",M18-X18)</f>
@@ -20536,7 +20536,7 @@
         <f>IF($K19="","",L19-M19-R19-S19-T19-U19-V19-W19)</f>
       </c>
       <c r="Z19" s="4">
-        <f>IF($K19="","",(Y19-AB19)/K19*100)</f>
+        <f>IF($K19="","",(Y19-AB19)/J19*100)</f>
       </c>
       <c r="AA19" s="4">
         <f>IF($K19="","",M19-X19)</f>
@@ -20587,7 +20587,7 @@
         <f>IF($K20="","",L20-M20-R20-S20-T20-U20-V20-W20)</f>
       </c>
       <c r="Z20" s="4">
-        <f>IF($K20="","",(Y20-AB20)/K20*100)</f>
+        <f>IF($K20="","",(Y20-AB20)/J20*100)</f>
       </c>
       <c r="AA20" s="4">
         <f>IF($K20="","",M20-X20)</f>
@@ -20638,7 +20638,7 @@
         <f>IF($K21="","",L21-M21-R21-S21-T21-U21-V21-W21)</f>
       </c>
       <c r="Z21" s="4">
-        <f>IF($K21="","",(Y21-AB21)/K21*100)</f>
+        <f>IF($K21="","",(Y21-AB21)/J21*100)</f>
       </c>
       <c r="AA21" s="4">
         <f>IF($K21="","",M21-X21)</f>
@@ -20689,7 +20689,7 @@
         <f>IF($K22="","",L22-M22-R22-S22-T22-U22-V22-W22)</f>
       </c>
       <c r="Z22" s="4">
-        <f>IF($K22="","",(Y22-AB22)/K22*100)</f>
+        <f>IF($K22="","",(Y22-AB22)/J22*100)</f>
       </c>
       <c r="AA22" s="4">
         <f>IF($K22="","",M22-X22)</f>
@@ -20740,7 +20740,7 @@
         <f>IF($K23="","",L23-M23-R23-S23-T23-U23-V23-W23)</f>
       </c>
       <c r="Z23" s="4">
-        <f>IF($K23="","",(Y23-AB23)/K23*100)</f>
+        <f>IF($K23="","",(Y23-AB23)/J23*100)</f>
       </c>
       <c r="AA23" s="4">
         <f>IF($K23="","",M23-X23)</f>
@@ -20791,7 +20791,7 @@
         <f>IF($K24="","",L24-M24-R24-S24-T24-U24-V24-W24)</f>
       </c>
       <c r="Z24" s="4">
-        <f>IF($K24="","",(Y24-AB24)/K24*100)</f>
+        <f>IF($K24="","",(Y24-AB24)/J24*100)</f>
       </c>
       <c r="AA24" s="4">
         <f>IF($K24="","",M24-X24)</f>
@@ -20842,7 +20842,7 @@
         <f>IF($K25="","",L25-M25-R25-S25-T25-U25-V25-W25)</f>
       </c>
       <c r="Z25" s="4">
-        <f>IF($K25="","",(Y25-AB25)/K25*100)</f>
+        <f>IF($K25="","",(Y25-AB25)/J25*100)</f>
       </c>
       <c r="AA25" s="4">
         <f>IF($K25="","",M25-X25)</f>
@@ -20893,7 +20893,7 @@
         <f>IF($K26="","",L26-M26-R26-S26-T26-U26-V26-W26)</f>
       </c>
       <c r="Z26" s="4">
-        <f>IF($K26="","",(Y26-AB26)/K26*100)</f>
+        <f>IF($K26="","",(Y26-AB26)/J26*100)</f>
       </c>
       <c r="AA26" s="4">
         <f>IF($K26="","",M26-X26)</f>
@@ -20944,7 +20944,7 @@
         <f>IF($K27="","",L27-M27-R27-S27-T27-U27-V27-W27)</f>
       </c>
       <c r="Z27" s="4">
-        <f>IF($K27="","",(Y27-AB27)/K27*100)</f>
+        <f>IF($K27="","",(Y27-AB27)/J27*100)</f>
       </c>
       <c r="AA27" s="4">
         <f>IF($K27="","",M27-X27)</f>
@@ -20995,7 +20995,7 @@
         <f>IF($K28="","",L28-M28-R28-S28-T28-U28-V28-W28)</f>
       </c>
       <c r="Z28" s="4">
-        <f>IF($K28="","",(Y28-AB28)/K28*100)</f>
+        <f>IF($K28="","",(Y28-AB28)/J28*100)</f>
       </c>
       <c r="AA28" s="4">
         <f>IF($K28="","",M28-X28)</f>
@@ -21046,7 +21046,7 @@
         <f>IF($K29="","",L29-M29-R29-S29-T29-U29-V29-W29)</f>
       </c>
       <c r="Z29" s="4">
-        <f>IF($K29="","",(Y29-AB29)/K29*100)</f>
+        <f>IF($K29="","",(Y29-AB29)/J29*100)</f>
       </c>
       <c r="AA29" s="4">
         <f>IF($K29="","",M29-X29)</f>
@@ -21097,7 +21097,7 @@
         <f>IF($K30="","",L30-M30-R30-S30-T30-U30-V30-W30)</f>
       </c>
       <c r="Z30" s="4">
-        <f>IF($K30="","",(Y30-AB30)/K30*100)</f>
+        <f>IF($K30="","",(Y30-AB30)/J30*100)</f>
       </c>
       <c r="AA30" s="4">
         <f>IF($K30="","",M30-X30)</f>
@@ -21148,7 +21148,7 @@
         <f>IF($K31="","",L31-M31-R31-S31-T31-U31-V31-W31)</f>
       </c>
       <c r="Z31" s="4">
-        <f>IF($K31="","",(Y31-AB31)/K31*100)</f>
+        <f>IF($K31="","",(Y31-AB31)/J31*100)</f>
       </c>
       <c r="AA31" s="4">
         <f>IF($K31="","",M31-X31)</f>
@@ -21199,7 +21199,7 @@
         <f>IF($K32="","",L32-M32-R32-S32-T32-U32-V32-W32)</f>
       </c>
       <c r="Z32" s="4">
-        <f>IF($K32="","",(Y32-AB32)/K32*100)</f>
+        <f>IF($K32="","",(Y32-AB32)/J32*100)</f>
       </c>
       <c r="AA32" s="4">
         <f>IF($K32="","",M32-X32)</f>
@@ -21250,7 +21250,7 @@
         <f>IF($K33="","",L33-M33-R33-S33-T33-U33-V33-W33)</f>
       </c>
       <c r="Z33" s="4">
-        <f>IF($K33="","",(Y33-AB33)/K33*100)</f>
+        <f>IF($K33="","",(Y33-AB33)/J33*100)</f>
       </c>
       <c r="AA33" s="4">
         <f>IF($K33="","",M33-X33)</f>
@@ -21301,7 +21301,7 @@
         <f>IF($K34="","",L34-M34-R34-S34-T34-U34-V34-W34)</f>
       </c>
       <c r="Z34" s="4">
-        <f>IF($K34="","",(Y34-AB34)/K34*100)</f>
+        <f>IF($K34="","",(Y34-AB34)/J34*100)</f>
       </c>
       <c r="AA34" s="4">
         <f>IF($K34="","",M34-X34)</f>
@@ -21352,7 +21352,7 @@
         <f>IF($K35="","",L35-M35-R35-S35-T35-U35-V35-W35)</f>
       </c>
       <c r="Z35" s="4">
-        <f>IF($K35="","",(Y35-AB35)/K35*100)</f>
+        <f>IF($K35="","",(Y35-AB35)/J35*100)</f>
       </c>
       <c r="AA35" s="4">
         <f>IF($K35="","",M35-X35)</f>
@@ -21403,7 +21403,7 @@
         <f>IF($K36="","",L36-M36-R36-S36-T36-U36-V36-W36)</f>
       </c>
       <c r="Z36" s="4">
-        <f>IF($K36="","",(Y36-AB36)/K36*100)</f>
+        <f>IF($K36="","",(Y36-AB36)/J36*100)</f>
       </c>
       <c r="AA36" s="4">
         <f>IF($K36="","",M36-X36)</f>
@@ -21454,7 +21454,7 @@
         <f>IF($K37="","",L37-M37-R37-S37-T37-U37-V37-W37)</f>
       </c>
       <c r="Z37" s="4">
-        <f>IF($K37="","",(Y37-AB37)/K37*100)</f>
+        <f>IF($K37="","",(Y37-AB37)/J37*100)</f>
       </c>
       <c r="AA37" s="4">
         <f>IF($K37="","",M37-X37)</f>
@@ -21505,7 +21505,7 @@
         <f>IF($K38="","",L38-M38-R38-S38-T38-U38-V38-W38)</f>
       </c>
       <c r="Z38" s="4">
-        <f>IF($K38="","",(Y38-AB38)/K38*100)</f>
+        <f>IF($K38="","",(Y38-AB38)/J38*100)</f>
       </c>
       <c r="AA38" s="4">
         <f>IF($K38="","",M38-X38)</f>
@@ -21556,7 +21556,7 @@
         <f>IF($K39="","",L39-M39-R39-S39-T39-U39-V39-W39)</f>
       </c>
       <c r="Z39" s="4">
-        <f>IF($K39="","",(Y39-AB39)/K39*100)</f>
+        <f>IF($K39="","",(Y39-AB39)/J39*100)</f>
       </c>
       <c r="AA39" s="4">
         <f>IF($K39="","",M39-X39)</f>
@@ -21607,7 +21607,7 @@
         <f>IF($K40="","",L40-M40-R40-S40-T40-U40-V40-W40)</f>
       </c>
       <c r="Z40" s="4">
-        <f>IF($K40="","",(Y40-AB40)/K40*100)</f>
+        <f>IF($K40="","",(Y40-AB40)/J40*100)</f>
       </c>
       <c r="AA40" s="4">
         <f>IF($K40="","",M40-X40)</f>
@@ -21658,7 +21658,7 @@
         <f>IF($K41="","",L41-M41-R41-S41-T41-U41-V41-W41)</f>
       </c>
       <c r="Z41" s="4">
-        <f>IF($K41="","",(Y41-AB41)/K41*100)</f>
+        <f>IF($K41="","",(Y41-AB41)/J41*100)</f>
       </c>
       <c r="AA41" s="4">
         <f>IF($K41="","",M41-X41)</f>
@@ -21709,7 +21709,7 @@
         <f>IF($K42="","",L42-M42-R42-S42-T42-U42-V42-W42)</f>
       </c>
       <c r="Z42" s="4">
-        <f>IF($K42="","",(Y42-AB42)/K42*100)</f>
+        <f>IF($K42="","",(Y42-AB42)/J42*100)</f>
       </c>
       <c r="AA42" s="4">
         <f>IF($K42="","",M42-X42)</f>
@@ -21760,7 +21760,7 @@
         <f>IF($K43="","",L43-M43-R43-S43-T43-U43-V43-W43)</f>
       </c>
       <c r="Z43" s="4">
-        <f>IF($K43="","",(Y43-AB43)/K43*100)</f>
+        <f>IF($K43="","",(Y43-AB43)/J43*100)</f>
       </c>
       <c r="AA43" s="4">
         <f>IF($K43="","",M43-X43)</f>
@@ -21811,7 +21811,7 @@
         <f>IF($K44="","",L44-M44-R44-S44-T44-U44-V44-W44)</f>
       </c>
       <c r="Z44" s="4">
-        <f>IF($K44="","",(Y44-AB44)/K44*100)</f>
+        <f>IF($K44="","",(Y44-AB44)/J44*100)</f>
       </c>
       <c r="AA44" s="4">
         <f>IF($K44="","",M44-X44)</f>
@@ -21862,7 +21862,7 @@
         <f>IF($K45="","",L45-M45-R45-S45-T45-U45-V45-W45)</f>
       </c>
       <c r="Z45" s="4">
-        <f>IF($K45="","",(Y45-AB45)/K45*100)</f>
+        <f>IF($K45="","",(Y45-AB45)/J45*100)</f>
       </c>
       <c r="AA45" s="4">
         <f>IF($K45="","",M45-X45)</f>
@@ -21913,7 +21913,7 @@
         <f>IF($K46="","",L46-M46-R46-S46-T46-U46-V46-W46)</f>
       </c>
       <c r="Z46" s="4">
-        <f>IF($K46="","",(Y46-AB46)/K46*100)</f>
+        <f>IF($K46="","",(Y46-AB46)/J46*100)</f>
       </c>
       <c r="AA46" s="4">
         <f>IF($K46="","",M46-X46)</f>
@@ -21964,7 +21964,7 @@
         <f>IF($K47="","",L47-M47-R47-S47-T47-U47-V47-W47)</f>
       </c>
       <c r="Z47" s="4">
-        <f>IF($K47="","",(Y47-AB47)/K47*100)</f>
+        <f>IF($K47="","",(Y47-AB47)/J47*100)</f>
       </c>
       <c r="AA47" s="4">
         <f>IF($K47="","",M47-X47)</f>
@@ -22015,7 +22015,7 @@
         <f>IF($K48="","",L48-M48-R48-S48-T48-U48-V48-W48)</f>
       </c>
       <c r="Z48" s="4">
-        <f>IF($K48="","",(Y48-AB48)/K48*100)</f>
+        <f>IF($K48="","",(Y48-AB48)/J48*100)</f>
       </c>
       <c r="AA48" s="4">
         <f>IF($K48="","",M48-X48)</f>
@@ -22066,7 +22066,7 @@
         <f>IF($K49="","",L49-M49-R49-S49-T49-U49-V49-W49)</f>
       </c>
       <c r="Z49" s="4">
-        <f>IF($K49="","",(Y49-AB49)/K49*100)</f>
+        <f>IF($K49="","",(Y49-AB49)/J49*100)</f>
       </c>
       <c r="AA49" s="4">
         <f>IF($K49="","",M49-X49)</f>
@@ -22117,7 +22117,7 @@
         <f>IF($K50="","",L50-M50-R50-S50-T50-U50-V50-W50)</f>
       </c>
       <c r="Z50" s="4">
-        <f>IF($K50="","",(Y50-AB50)/K50*100)</f>
+        <f>IF($K50="","",(Y50-AB50)/J50*100)</f>
       </c>
       <c r="AA50" s="4">
         <f>IF($K50="","",M50-X50)</f>
@@ -22168,7 +22168,7 @@
         <f>IF($K51="","",L51-M51-R51-S51-T51-U51-V51-W51)</f>
       </c>
       <c r="Z51" s="4">
-        <f>IF($K51="","",(Y51-AB51)/K51*100)</f>
+        <f>IF($K51="","",(Y51-AB51)/J51*100)</f>
       </c>
       <c r="AA51" s="4">
         <f>IF($K51="","",M51-X51)</f>
@@ -22219,7 +22219,7 @@
         <f>IF($K52="","",L52-M52-R52-S52-T52-U52-V52-W52)</f>
       </c>
       <c r="Z52" s="4">
-        <f>IF($K52="","",(Y52-AB52)/K52*100)</f>
+        <f>IF($K52="","",(Y52-AB52)/J52*100)</f>
       </c>
       <c r="AA52" s="4">
         <f>IF($K52="","",M52-X52)</f>
@@ -22270,7 +22270,7 @@
         <f>IF($K53="","",L53-M53-R53-S53-T53-U53-V53-W53)</f>
       </c>
       <c r="Z53" s="4">
-        <f>IF($K53="","",(Y53-AB53)/K53*100)</f>
+        <f>IF($K53="","",(Y53-AB53)/J53*100)</f>
       </c>
       <c r="AA53" s="4">
         <f>IF($K53="","",M53-X53)</f>
@@ -22321,7 +22321,7 @@
         <f>IF($K54="","",L54-M54-R54-S54-T54-U54-V54-W54)</f>
       </c>
       <c r="Z54" s="4">
-        <f>IF($K54="","",(Y54-AB54)/K54*100)</f>
+        <f>IF($K54="","",(Y54-AB54)/J54*100)</f>
       </c>
       <c r="AA54" s="4">
         <f>IF($K54="","",M54-X54)</f>
@@ -22372,7 +22372,7 @@
         <f>IF($K55="","",L55-M55-R55-S55-T55-U55-V55-W55)</f>
       </c>
       <c r="Z55" s="4">
-        <f>IF($K55="","",(Y55-AB55)/K55*100)</f>
+        <f>IF($K55="","",(Y55-AB55)/J55*100)</f>
       </c>
       <c r="AA55" s="4">
         <f>IF($K55="","",M55-X55)</f>
@@ -22423,7 +22423,7 @@
         <f>IF($K56="","",L56-M56-R56-S56-T56-U56-V56-W56)</f>
       </c>
       <c r="Z56" s="4">
-        <f>IF($K56="","",(Y56-AB56)/K56*100)</f>
+        <f>IF($K56="","",(Y56-AB56)/J56*100)</f>
       </c>
       <c r="AA56" s="4">
         <f>IF($K56="","",M56-X56)</f>
@@ -22474,7 +22474,7 @@
         <f>IF($K57="","",L57-M57-R57-S57-T57-U57-V57-W57)</f>
       </c>
       <c r="Z57" s="4">
-        <f>IF($K57="","",(Y57-AB57)/K57*100)</f>
+        <f>IF($K57="","",(Y57-AB57)/J57*100)</f>
       </c>
       <c r="AA57" s="4">
         <f>IF($K57="","",M57-X57)</f>
@@ -22525,7 +22525,7 @@
         <f>IF($K58="","",L58-M58-R58-S58-T58-U58-V58-W58)</f>
       </c>
       <c r="Z58" s="4">
-        <f>IF($K58="","",(Y58-AB58)/K58*100)</f>
+        <f>IF($K58="","",(Y58-AB58)/J58*100)</f>
       </c>
       <c r="AA58" s="4">
         <f>IF($K58="","",M58-X58)</f>
@@ -22576,7 +22576,7 @@
         <f>IF($K59="","",L59-M59-R59-S59-T59-U59-V59-W59)</f>
       </c>
       <c r="Z59" s="4">
-        <f>IF($K59="","",(Y59-AB59)/K59*100)</f>
+        <f>IF($K59="","",(Y59-AB59)/J59*100)</f>
       </c>
       <c r="AA59" s="4">
         <f>IF($K59="","",M59-X59)</f>
@@ -22627,7 +22627,7 @@
         <f>IF($K60="","",L60-M60-R60-S60-T60-U60-V60-W60)</f>
       </c>
       <c r="Z60" s="4">
-        <f>IF($K60="","",(Y60-AB60)/K60*100)</f>
+        <f>IF($K60="","",(Y60-AB60)/J60*100)</f>
       </c>
       <c r="AA60" s="4">
         <f>IF($K60="","",M60-X60)</f>
@@ -22678,7 +22678,7 @@
         <f>IF($K61="","",L61-M61-R61-S61-T61-U61-V61-W61)</f>
       </c>
       <c r="Z61" s="4">
-        <f>IF($K61="","",(Y61-AB61)/K61*100)</f>
+        <f>IF($K61="","",(Y61-AB61)/J61*100)</f>
       </c>
       <c r="AA61" s="4">
         <f>IF($K61="","",M61-X61)</f>
@@ -22729,7 +22729,7 @@
         <f>IF($K62="","",L62-M62-R62-S62-T62-U62-V62-W62)</f>
       </c>
       <c r="Z62" s="4">
-        <f>IF($K62="","",(Y62-AB62)/K62*100)</f>
+        <f>IF($K62="","",(Y62-AB62)/J62*100)</f>
       </c>
       <c r="AA62" s="4">
         <f>IF($K62="","",M62-X62)</f>
@@ -22780,7 +22780,7 @@
         <f>IF($K63="","",L63-M63-R63-S63-T63-U63-V63-W63)</f>
       </c>
       <c r="Z63" s="4">
-        <f>IF($K63="","",(Y63-AB63)/K63*100)</f>
+        <f>IF($K63="","",(Y63-AB63)/J63*100)</f>
       </c>
       <c r="AA63" s="4">
         <f>IF($K63="","",M63-X63)</f>
@@ -22831,7 +22831,7 @@
         <f>IF($K64="","",L64-M64-R64-S64-T64-U64-V64-W64)</f>
       </c>
       <c r="Z64" s="4">
-        <f>IF($K64="","",(Y64-AB64)/K64*100)</f>
+        <f>IF($K64="","",(Y64-AB64)/J64*100)</f>
       </c>
       <c r="AA64" s="4">
         <f>IF($K64="","",M64-X64)</f>
@@ -22882,7 +22882,7 @@
         <f>IF($K65="","",L65-M65-R65-S65-T65-U65-V65-W65)</f>
       </c>
       <c r="Z65" s="4">
-        <f>IF($K65="","",(Y65-AB65)/K65*100)</f>
+        <f>IF($K65="","",(Y65-AB65)/J65*100)</f>
       </c>
       <c r="AA65" s="4">
         <f>IF($K65="","",M65-X65)</f>
@@ -22933,7 +22933,7 @@
         <f>IF($K66="","",L66-M66-R66-S66-T66-U66-V66-W66)</f>
       </c>
       <c r="Z66" s="4">
-        <f>IF($K66="","",(Y66-AB66)/K66*100)</f>
+        <f>IF($K66="","",(Y66-AB66)/J66*100)</f>
       </c>
       <c r="AA66" s="4">
         <f>IF($K66="","",M66-X66)</f>
@@ -22984,7 +22984,7 @@
         <f>IF($K67="","",L67-M67-R67-S67-T67-U67-V67-W67)</f>
       </c>
       <c r="Z67" s="4">
-        <f>IF($K67="","",(Y67-AB67)/K67*100)</f>
+        <f>IF($K67="","",(Y67-AB67)/J67*100)</f>
       </c>
       <c r="AA67" s="4">
         <f>IF($K67="","",M67-X67)</f>
@@ -23035,7 +23035,7 @@
         <f>IF($K68="","",L68-M68-R68-S68-T68-U68-V68-W68)</f>
       </c>
       <c r="Z68" s="4">
-        <f>IF($K68="","",(Y68-AB68)/K68*100)</f>
+        <f>IF($K68="","",(Y68-AB68)/J68*100)</f>
       </c>
       <c r="AA68" s="4">
         <f>IF($K68="","",M68-X68)</f>
@@ -23086,7 +23086,7 @@
         <f>IF($K69="","",L69-M69-R69-S69-T69-U69-V69-W69)</f>
       </c>
       <c r="Z69" s="4">
-        <f>IF($K69="","",(Y69-AB69)/K69*100)</f>
+        <f>IF($K69="","",(Y69-AB69)/J69*100)</f>
       </c>
       <c r="AA69" s="4">
         <f>IF($K69="","",M69-X69)</f>
@@ -23137,7 +23137,7 @@
         <f>IF($K70="","",L70-M70-R70-S70-T70-U70-V70-W70)</f>
       </c>
       <c r="Z70" s="4">
-        <f>IF($K70="","",(Y70-AB70)/K70*100)</f>
+        <f>IF($K70="","",(Y70-AB70)/J70*100)</f>
       </c>
       <c r="AA70" s="4">
         <f>IF($K70="","",M70-X70)</f>
@@ -23188,7 +23188,7 @@
         <f>IF($K71="","",L71-M71-R71-S71-T71-U71-V71-W71)</f>
       </c>
       <c r="Z71" s="4">
-        <f>IF($K71="","",(Y71-AB71)/K71*100)</f>
+        <f>IF($K71="","",(Y71-AB71)/J71*100)</f>
       </c>
       <c r="AA71" s="4">
         <f>IF($K71="","",M71-X71)</f>
@@ -23239,7 +23239,7 @@
         <f>IF($K72="","",L72-M72-R72-S72-T72-U72-V72-W72)</f>
       </c>
       <c r="Z72" s="4">
-        <f>IF($K72="","",(Y72-AB72)/K72*100)</f>
+        <f>IF($K72="","",(Y72-AB72)/J72*100)</f>
       </c>
       <c r="AA72" s="4">
         <f>IF($K72="","",M72-X72)</f>
@@ -23290,7 +23290,7 @@
         <f>IF($K73="","",L73-M73-R73-S73-T73-U73-V73-W73)</f>
       </c>
       <c r="Z73" s="4">
-        <f>IF($K73="","",(Y73-AB73)/K73*100)</f>
+        <f>IF($K73="","",(Y73-AB73)/J73*100)</f>
       </c>
       <c r="AA73" s="4">
         <f>IF($K73="","",M73-X73)</f>
@@ -23341,7 +23341,7 @@
         <f>IF($K74="","",L74-M74-R74-S74-T74-U74-V74-W74)</f>
       </c>
       <c r="Z74" s="4">
-        <f>IF($K74="","",(Y74-AB74)/K74*100)</f>
+        <f>IF($K74="","",(Y74-AB74)/J74*100)</f>
       </c>
       <c r="AA74" s="4">
         <f>IF($K74="","",M74-X74)</f>
@@ -23392,7 +23392,7 @@
         <f>IF($K75="","",L75-M75-R75-S75-T75-U75-V75-W75)</f>
       </c>
       <c r="Z75" s="4">
-        <f>IF($K75="","",(Y75-AB75)/K75*100)</f>
+        <f>IF($K75="","",(Y75-AB75)/J75*100)</f>
       </c>
       <c r="AA75" s="4">
         <f>IF($K75="","",M75-X75)</f>
@@ -23443,7 +23443,7 @@
         <f>IF($K76="","",L76-M76-R76-S76-T76-U76-V76-W76)</f>
       </c>
       <c r="Z76" s="4">
-        <f>IF($K76="","",(Y76-AB76)/K76*100)</f>
+        <f>IF($K76="","",(Y76-AB76)/J76*100)</f>
       </c>
       <c r="AA76" s="4">
         <f>IF($K76="","",M76-X76)</f>
@@ -23494,7 +23494,7 @@
         <f>IF($K77="","",L77-M77-R77-S77-T77-U77-V77-W77)</f>
       </c>
       <c r="Z77" s="4">
-        <f>IF($K77="","",(Y77-AB77)/K77*100)</f>
+        <f>IF($K77="","",(Y77-AB77)/J77*100)</f>
       </c>
       <c r="AA77" s="4">
         <f>IF($K77="","",M77-X77)</f>
@@ -23545,7 +23545,7 @@
         <f>IF($K78="","",L78-M78-R78-S78-T78-U78-V78-W78)</f>
       </c>
       <c r="Z78" s="4">
-        <f>IF($K78="","",(Y78-AB78)/K78*100)</f>
+        <f>IF($K78="","",(Y78-AB78)/J78*100)</f>
       </c>
       <c r="AA78" s="4">
         <f>IF($K78="","",M78-X78)</f>
@@ -23596,7 +23596,7 @@
         <f>IF($K79="","",L79-M79-R79-S79-T79-U79-V79-W79)</f>
       </c>
       <c r="Z79" s="4">
-        <f>IF($K79="","",(Y79-AB79)/K79*100)</f>
+        <f>IF($K79="","",(Y79-AB79)/J79*100)</f>
       </c>
       <c r="AA79" s="4">
         <f>IF($K79="","",M79-X79)</f>
@@ -23647,7 +23647,7 @@
         <f>IF($K80="","",L80-M80-R80-S80-T80-U80-V80-W80)</f>
       </c>
       <c r="Z80" s="4">
-        <f>IF($K80="","",(Y80-AB80)/K80*100)</f>
+        <f>IF($K80="","",(Y80-AB80)/J80*100)</f>
       </c>
       <c r="AA80" s="4">
         <f>IF($K80="","",M80-X80)</f>
@@ -23698,7 +23698,7 @@
         <f>IF($K81="","",L81-M81-R81-S81-T81-U81-V81-W81)</f>
       </c>
       <c r="Z81" s="4">
-        <f>IF($K81="","",(Y81-AB81)/K81*100)</f>
+        <f>IF($K81="","",(Y81-AB81)/J81*100)</f>
       </c>
       <c r="AA81" s="4">
         <f>IF($K81="","",M81-X81)</f>
@@ -23749,7 +23749,7 @@
         <f>IF($K82="","",L82-M82-R82-S82-T82-U82-V82-W82)</f>
       </c>
       <c r="Z82" s="4">
-        <f>IF($K82="","",(Y82-AB82)/K82*100)</f>
+        <f>IF($K82="","",(Y82-AB82)/J82*100)</f>
       </c>
       <c r="AA82" s="4">
         <f>IF($K82="","",M82-X82)</f>
@@ -23800,7 +23800,7 @@
         <f>IF($K83="","",L83-M83-R83-S83-T83-U83-V83-W83)</f>
       </c>
       <c r="Z83" s="4">
-        <f>IF($K83="","",(Y83-AB83)/K83*100)</f>
+        <f>IF($K83="","",(Y83-AB83)/J83*100)</f>
       </c>
       <c r="AA83" s="4">
         <f>IF($K83="","",M83-X83)</f>
@@ -23851,7 +23851,7 @@
         <f>IF($K84="","",L84-M84-R84-S84-T84-U84-V84-W84)</f>
       </c>
       <c r="Z84" s="4">
-        <f>IF($K84="","",(Y84-AB84)/K84*100)</f>
+        <f>IF($K84="","",(Y84-AB84)/J84*100)</f>
       </c>
       <c r="AA84" s="4">
         <f>IF($K84="","",M84-X84)</f>
@@ -23902,7 +23902,7 @@
         <f>IF($K85="","",L85-M85-R85-S85-T85-U85-V85-W85)</f>
       </c>
       <c r="Z85" s="4">
-        <f>IF($K85="","",(Y85-AB85)/K85*100)</f>
+        <f>IF($K85="","",(Y85-AB85)/J85*100)</f>
       </c>
       <c r="AA85" s="4">
         <f>IF($K85="","",M85-X85)</f>
@@ -23953,7 +23953,7 @@
         <f>IF($K86="","",L86-M86-R86-S86-T86-U86-V86-W86)</f>
       </c>
       <c r="Z86" s="4">
-        <f>IF($K86="","",(Y86-AB86)/K86*100)</f>
+        <f>IF($K86="","",(Y86-AB86)/J86*100)</f>
       </c>
       <c r="AA86" s="4">
         <f>IF($K86="","",M86-X86)</f>
@@ -24004,7 +24004,7 @@
         <f>IF($K87="","",L87-M87-R87-S87-T87-U87-V87-W87)</f>
       </c>
       <c r="Z87" s="4">
-        <f>IF($K87="","",(Y87-AB87)/K87*100)</f>
+        <f>IF($K87="","",(Y87-AB87)/J87*100)</f>
       </c>
       <c r="AA87" s="4">
         <f>IF($K87="","",M87-X87)</f>
@@ -24055,7 +24055,7 @@
         <f>IF($K88="","",L88-M88-R88-S88-T88-U88-V88-W88)</f>
       </c>
       <c r="Z88" s="4">
-        <f>IF($K88="","",(Y88-AB88)/K88*100)</f>
+        <f>IF($K88="","",(Y88-AB88)/J88*100)</f>
       </c>
       <c r="AA88" s="4">
         <f>IF($K88="","",M88-X88)</f>
@@ -24106,7 +24106,7 @@
         <f>IF($K89="","",L89-M89-R89-S89-T89-U89-V89-W89)</f>
       </c>
       <c r="Z89" s="4">
-        <f>IF($K89="","",(Y89-AB89)/K89*100)</f>
+        <f>IF($K89="","",(Y89-AB89)/J89*100)</f>
       </c>
       <c r="AA89" s="4">
         <f>IF($K89="","",M89-X89)</f>
@@ -24157,7 +24157,7 @@
         <f>IF($K90="","",L90-M90-R90-S90-T90-U90-V90-W90)</f>
       </c>
       <c r="Z90" s="4">
-        <f>IF($K90="","",(Y90-AB90)/K90*100)</f>
+        <f>IF($K90="","",(Y90-AB90)/J90*100)</f>
       </c>
       <c r="AA90" s="4">
         <f>IF($K90="","",M90-X90)</f>
@@ -24208,7 +24208,7 @@
         <f>IF($K91="","",L91-M91-R91-S91-T91-U91-V91-W91)</f>
       </c>
       <c r="Z91" s="4">
-        <f>IF($K91="","",(Y91-AB91)/K91*100)</f>
+        <f>IF($K91="","",(Y91-AB91)/J91*100)</f>
       </c>
       <c r="AA91" s="4">
         <f>IF($K91="","",M91-X91)</f>
@@ -24259,7 +24259,7 @@
         <f>IF($K92="","",L92-M92-R92-S92-T92-U92-V92-W92)</f>
       </c>
       <c r="Z92" s="4">
-        <f>IF($K92="","",(Y92-AB92)/K92*100)</f>
+        <f>IF($K92="","",(Y92-AB92)/J92*100)</f>
       </c>
       <c r="AA92" s="4">
         <f>IF($K92="","",M92-X92)</f>
@@ -24310,7 +24310,7 @@
         <f>IF($K93="","",L93-M93-R93-S93-T93-U93-V93-W93)</f>
       </c>
       <c r="Z93" s="4">
-        <f>IF($K93="","",(Y93-AB93)/K93*100)</f>
+        <f>IF($K93="","",(Y93-AB93)/J93*100)</f>
       </c>
       <c r="AA93" s="4">
         <f>IF($K93="","",M93-X93)</f>
@@ -24361,7 +24361,7 @@
         <f>IF($K94="","",L94-M94-R94-S94-T94-U94-V94-W94)</f>
       </c>
       <c r="Z94" s="4">
-        <f>IF($K94="","",(Y94-AB94)/K94*100)</f>
+        <f>IF($K94="","",(Y94-AB94)/J94*100)</f>
       </c>
       <c r="AA94" s="4">
         <f>IF($K94="","",M94-X94)</f>
@@ -24412,7 +24412,7 @@
         <f>IF($K95="","",L95-M95-R95-S95-T95-U95-V95-W95)</f>
       </c>
       <c r="Z95" s="4">
-        <f>IF($K95="","",(Y95-AB95)/K95*100)</f>
+        <f>IF($K95="","",(Y95-AB95)/J95*100)</f>
       </c>
       <c r="AA95" s="4">
         <f>IF($K95="","",M95-X95)</f>
@@ -24463,7 +24463,7 @@
         <f>IF($K96="","",L96-M96-R96-S96-T96-U96-V96-W96)</f>
       </c>
       <c r="Z96" s="4">
-        <f>IF($K96="","",(Y96-AB96)/K96*100)</f>
+        <f>IF($K96="","",(Y96-AB96)/J96*100)</f>
       </c>
       <c r="AA96" s="4">
         <f>IF($K96="","",M96-X96)</f>
@@ -24514,7 +24514,7 @@
         <f>IF($K97="","",L97-M97-R97-S97-T97-U97-V97-W97)</f>
       </c>
       <c r="Z97" s="4">
-        <f>IF($K97="","",(Y97-AB97)/K97*100)</f>
+        <f>IF($K97="","",(Y97-AB97)/J97*100)</f>
       </c>
       <c r="AA97" s="4">
         <f>IF($K97="","",M97-X97)</f>
@@ -24565,7 +24565,7 @@
         <f>IF($K98="","",L98-M98-R98-S98-T98-U98-V98-W98)</f>
       </c>
       <c r="Z98" s="4">
-        <f>IF($K98="","",(Y98-AB98)/K98*100)</f>
+        <f>IF($K98="","",(Y98-AB98)/J98*100)</f>
       </c>
       <c r="AA98" s="4">
         <f>IF($K98="","",M98-X98)</f>
@@ -24616,7 +24616,7 @@
         <f>IF($K99="","",L99-M99-R99-S99-T99-U99-V99-W99)</f>
       </c>
       <c r="Z99" s="4">
-        <f>IF($K99="","",(Y99-AB99)/K99*100)</f>
+        <f>IF($K99="","",(Y99-AB99)/J99*100)</f>
       </c>
       <c r="AA99" s="4">
         <f>IF($K99="","",M99-X99)</f>
@@ -24667,7 +24667,7 @@
         <f>IF($K100="","",L100-M100-R100-S100-T100-U100-V100-W100)</f>
       </c>
       <c r="Z100" s="4">
-        <f>IF($K100="","",(Y100-AB100)/K100*100)</f>
+        <f>IF($K100="","",(Y100-AB100)/J100*100)</f>
       </c>
       <c r="AA100" s="4">
         <f>IF($K100="","",M100-X100)</f>
@@ -24718,7 +24718,7 @@
         <f>IF($K101="","",L101-M101-R101-S101-T101-U101-V101-W101)</f>
       </c>
       <c r="Z101" s="4">
-        <f>IF($K101="","",(Y101-AB101)/K101*100)</f>
+        <f>IF($K101="","",(Y101-AB101)/J101*100)</f>
       </c>
       <c r="AA101" s="4">
         <f>IF($K101="","",M101-X101)</f>
@@ -24769,7 +24769,7 @@
         <f>IF($K102="","",L102-M102-R102-S102-T102-U102-V102-W102)</f>
       </c>
       <c r="Z102" s="4">
-        <f>IF($K102="","",(Y102-AB102)/K102*100)</f>
+        <f>IF($K102="","",(Y102-AB102)/J102*100)</f>
       </c>
       <c r="AA102" s="4">
         <f>IF($K102="","",M102-X102)</f>
@@ -24820,7 +24820,7 @@
         <f>IF($K103="","",L103-M103-R103-S103-T103-U103-V103-W103)</f>
       </c>
       <c r="Z103" s="4">
-        <f>IF($K103="","",(Y103-AB103)/K103*100)</f>
+        <f>IF($K103="","",(Y103-AB103)/J103*100)</f>
       </c>
       <c r="AA103" s="4">
         <f>IF($K103="","",M103-X103)</f>
@@ -24871,7 +24871,7 @@
         <f>IF($K104="","",L104-M104-R104-S104-T104-U104-V104-W104)</f>
       </c>
       <c r="Z104" s="4">
-        <f>IF($K104="","",(Y104-AB104)/K104*100)</f>
+        <f>IF($K104="","",(Y104-AB104)/J104*100)</f>
       </c>
       <c r="AA104" s="4">
         <f>IF($K104="","",M104-X104)</f>
@@ -24922,7 +24922,7 @@
         <f>IF($K105="","",L105-M105-R105-S105-T105-U105-V105-W105)</f>
       </c>
       <c r="Z105" s="4">
-        <f>IF($K105="","",(Y105-AB105)/K105*100)</f>
+        <f>IF($K105="","",(Y105-AB105)/J105*100)</f>
       </c>
       <c r="AA105" s="4">
         <f>IF($K105="","",M105-X105)</f>
@@ -24973,7 +24973,7 @@
         <f>IF($K106="","",L106-M106-R106-S106-T106-U106-V106-W106)</f>
       </c>
       <c r="Z106" s="4">
-        <f>IF($K106="","",(Y106-AB106)/K106*100)</f>
+        <f>IF($K106="","",(Y106-AB106)/J106*100)</f>
       </c>
       <c r="AA106" s="4">
         <f>IF($K106="","",M106-X106)</f>
@@ -25024,7 +25024,7 @@
         <f>IF($K107="","",L107-M107-R107-S107-T107-U107-V107-W107)</f>
       </c>
       <c r="Z107" s="4">
-        <f>IF($K107="","",(Y107-AB107)/K107*100)</f>
+        <f>IF($K107="","",(Y107-AB107)/J107*100)</f>
       </c>
       <c r="AA107" s="4">
         <f>IF($K107="","",M107-X107)</f>
@@ -25075,7 +25075,7 @@
         <f>IF($K108="","",L108-M108-R108-S108-T108-U108-V108-W108)</f>
       </c>
       <c r="Z108" s="4">
-        <f>IF($K108="","",(Y108-AB108)/K108*100)</f>
+        <f>IF($K108="","",(Y108-AB108)/J108*100)</f>
       </c>
       <c r="AA108" s="4">
         <f>IF($K108="","",M108-X108)</f>
@@ -25126,7 +25126,7 @@
         <f>IF($K109="","",L109-M109-R109-S109-T109-U109-V109-W109)</f>
       </c>
       <c r="Z109" s="4">
-        <f>IF($K109="","",(Y109-AB109)/K109*100)</f>
+        <f>IF($K109="","",(Y109-AB109)/J109*100)</f>
       </c>
       <c r="AA109" s="4">
         <f>IF($K109="","",M109-X109)</f>
@@ -25177,7 +25177,7 @@
         <f>IF($K110="","",L110-M110-R110-S110-T110-U110-V110-W110)</f>
       </c>
       <c r="Z110" s="4">
-        <f>IF($K110="","",(Y110-AB110)/K110*100)</f>
+        <f>IF($K110="","",(Y110-AB110)/J110*100)</f>
       </c>
       <c r="AA110" s="4">
         <f>IF($K110="","",M110-X110)</f>
@@ -25228,7 +25228,7 @@
         <f>IF($K111="","",L111-M111-R111-S111-T111-U111-V111-W111)</f>
       </c>
       <c r="Z111" s="4">
-        <f>IF($K111="","",(Y111-AB111)/K111*100)</f>
+        <f>IF($K111="","",(Y111-AB111)/J111*100)</f>
       </c>
       <c r="AA111" s="4">
         <f>IF($K111="","",M111-X111)</f>
@@ -25279,7 +25279,7 @@
         <f>IF($K112="","",L112-M112-R112-S112-T112-U112-V112-W112)</f>
       </c>
       <c r="Z112" s="4">
-        <f>IF($K112="","",(Y112-AB112)/K112*100)</f>
+        <f>IF($K112="","",(Y112-AB112)/J112*100)</f>
       </c>
       <c r="AA112" s="4">
         <f>IF($K112="","",M112-X112)</f>
@@ -25330,7 +25330,7 @@
         <f>IF($K113="","",L113-M113-R113-S113-T113-U113-V113-W113)</f>
       </c>
       <c r="Z113" s="4">
-        <f>IF($K113="","",(Y113-AB113)/K113*100)</f>
+        <f>IF($K113="","",(Y113-AB113)/J113*100)</f>
       </c>
       <c r="AA113" s="4">
         <f>IF($K113="","",M113-X113)</f>
@@ -25381,7 +25381,7 @@
         <f>IF($K114="","",L114-M114-R114-S114-T114-U114-V114-W114)</f>
       </c>
       <c r="Z114" s="4">
-        <f>IF($K114="","",(Y114-AB114)/K114*100)</f>
+        <f>IF($K114="","",(Y114-AB114)/J114*100)</f>
       </c>
       <c r="AA114" s="4">
         <f>IF($K114="","",M114-X114)</f>
@@ -25432,7 +25432,7 @@
         <f>IF($K115="","",L115-M115-R115-S115-T115-U115-V115-W115)</f>
       </c>
       <c r="Z115" s="4">
-        <f>IF($K115="","",(Y115-AB115)/K115*100)</f>
+        <f>IF($K115="","",(Y115-AB115)/J115*100)</f>
       </c>
       <c r="AA115" s="4">
         <f>IF($K115="","",M115-X115)</f>
@@ -25483,7 +25483,7 @@
         <f>IF($K116="","",L116-M116-R116-S116-T116-U116-V116-W116)</f>
       </c>
       <c r="Z116" s="4">
-        <f>IF($K116="","",(Y116-AB116)/K116*100)</f>
+        <f>IF($K116="","",(Y116-AB116)/J116*100)</f>
       </c>
       <c r="AA116" s="4">
         <f>IF($K116="","",M116-X116)</f>
@@ -25534,7 +25534,7 @@
         <f>IF($K117="","",L117-M117-R117-S117-T117-U117-V117-W117)</f>
       </c>
       <c r="Z117" s="4">
-        <f>IF($K117="","",(Y117-AB117)/K117*100)</f>
+        <f>IF($K117="","",(Y117-AB117)/J117*100)</f>
       </c>
       <c r="AA117" s="4">
         <f>IF($K117="","",M117-X117)</f>
@@ -25585,7 +25585,7 @@
         <f>IF($K118="","",L118-M118-R118-S118-T118-U118-V118-W118)</f>
       </c>
       <c r="Z118" s="4">
-        <f>IF($K118="","",(Y118-AB118)/K118*100)</f>
+        <f>IF($K118="","",(Y118-AB118)/J118*100)</f>
       </c>
       <c r="AA118" s="4">
         <f>IF($K118="","",M118-X118)</f>
@@ -25636,7 +25636,7 @@
         <f>IF($K119="","",L119-M119-R119-S119-T119-U119-V119-W119)</f>
       </c>
       <c r="Z119" s="4">
-        <f>IF($K119="","",(Y119-AB119)/K119*100)</f>
+        <f>IF($K119="","",(Y119-AB119)/J119*100)</f>
       </c>
       <c r="AA119" s="4">
         <f>IF($K119="","",M119-X119)</f>
@@ -25687,7 +25687,7 @@
         <f>IF($K120="","",L120-M120-R120-S120-T120-U120-V120-W120)</f>
       </c>
       <c r="Z120" s="4">
-        <f>IF($K120="","",(Y120-AB120)/K120*100)</f>
+        <f>IF($K120="","",(Y120-AB120)/J120*100)</f>
       </c>
       <c r="AA120" s="4">
         <f>IF($K120="","",M120-X120)</f>
@@ -25738,7 +25738,7 @@
         <f>IF($K121="","",L121-M121-R121-S121-T121-U121-V121-W121)</f>
       </c>
       <c r="Z121" s="4">
-        <f>IF($K121="","",(Y121-AB121)/K121*100)</f>
+        <f>IF($K121="","",(Y121-AB121)/J121*100)</f>
       </c>
       <c r="AA121" s="4">
         <f>IF($K121="","",M121-X121)</f>
@@ -25789,7 +25789,7 @@
         <f>IF($K122="","",L122-M122-R122-S122-T122-U122-V122-W122)</f>
       </c>
       <c r="Z122" s="4">
-        <f>IF($K122="","",(Y122-AB122)/K122*100)</f>
+        <f>IF($K122="","",(Y122-AB122)/J122*100)</f>
       </c>
       <c r="AA122" s="4">
         <f>IF($K122="","",M122-X122)</f>
@@ -25840,7 +25840,7 @@
         <f>IF($K123="","",L123-M123-R123-S123-T123-U123-V123-W123)</f>
       </c>
       <c r="Z123" s="4">
-        <f>IF($K123="","",(Y123-AB123)/K123*100)</f>
+        <f>IF($K123="","",(Y123-AB123)/J123*100)</f>
       </c>
       <c r="AA123" s="4">
         <f>IF($K123="","",M123-X123)</f>
@@ -25891,7 +25891,7 @@
         <f>IF($K124="","",L124-M124-R124-S124-T124-U124-V124-W124)</f>
       </c>
       <c r="Z124" s="4">
-        <f>IF($K124="","",(Y124-AB124)/K124*100)</f>
+        <f>IF($K124="","",(Y124-AB124)/J124*100)</f>
       </c>
       <c r="AA124" s="4">
         <f>IF($K124="","",M124-X124)</f>
@@ -25942,7 +25942,7 @@
         <f>IF($K125="","",L125-M125-R125-S125-T125-U125-V125-W125)</f>
       </c>
       <c r="Z125" s="4">
-        <f>IF($K125="","",(Y125-AB125)/K125*100)</f>
+        <f>IF($K125="","",(Y125-AB125)/J125*100)</f>
       </c>
       <c r="AA125" s="4">
         <f>IF($K125="","",M125-X125)</f>
@@ -25993,7 +25993,7 @@
         <f>IF($K126="","",L126-M126-R126-S126-T126-U126-V126-W126)</f>
       </c>
       <c r="Z126" s="4">
-        <f>IF($K126="","",(Y126-AB126)/K126*100)</f>
+        <f>IF($K126="","",(Y126-AB126)/J126*100)</f>
       </c>
       <c r="AA126" s="4">
         <f>IF($K126="","",M126-X126)</f>
@@ -26044,7 +26044,7 @@
         <f>IF($K127="","",L127-M127-R127-S127-T127-U127-V127-W127)</f>
       </c>
       <c r="Z127" s="4">
-        <f>IF($K127="","",(Y127-AB127)/K127*100)</f>
+        <f>IF($K127="","",(Y127-AB127)/J127*100)</f>
       </c>
       <c r="AA127" s="4">
         <f>IF($K127="","",M127-X127)</f>
@@ -26095,7 +26095,7 @@
         <f>IF($K128="","",L128-M128-R128-S128-T128-U128-V128-W128)</f>
       </c>
       <c r="Z128" s="4">
-        <f>IF($K128="","",(Y128-AB128)/K128*100)</f>
+        <f>IF($K128="","",(Y128-AB128)/J128*100)</f>
       </c>
       <c r="AA128" s="4">
         <f>IF($K128="","",M128-X128)</f>
@@ -26146,7 +26146,7 @@
         <f>IF($K129="","",L129-M129-R129-S129-T129-U129-V129-W129)</f>
       </c>
       <c r="Z129" s="4">
-        <f>IF($K129="","",(Y129-AB129)/K129*100)</f>
+        <f>IF($K129="","",(Y129-AB129)/J129*100)</f>
       </c>
       <c r="AA129" s="4">
         <f>IF($K129="","",M129-X129)</f>
@@ -26197,7 +26197,7 @@
         <f>IF($K130="","",L130-M130-R130-S130-T130-U130-V130-W130)</f>
       </c>
       <c r="Z130" s="4">
-        <f>IF($K130="","",(Y130-AB130)/K130*100)</f>
+        <f>IF($K130="","",(Y130-AB130)/J130*100)</f>
       </c>
       <c r="AA130" s="4">
         <f>IF($K130="","",M130-X130)</f>
@@ -26248,7 +26248,7 @@
         <f>IF($K131="","",L131-M131-R131-S131-T131-U131-V131-W131)</f>
       </c>
       <c r="Z131" s="4">
-        <f>IF($K131="","",(Y131-AB131)/K131*100)</f>
+        <f>IF($K131="","",(Y131-AB131)/J131*100)</f>
       </c>
       <c r="AA131" s="4">
         <f>IF($K131="","",M131-X131)</f>
@@ -26299,7 +26299,7 @@
         <f>IF($K132="","",L132-M132-R132-S132-T132-U132-V132-W132)</f>
       </c>
       <c r="Z132" s="4">
-        <f>IF($K132="","",(Y132-AB132)/K132*100)</f>
+        <f>IF($K132="","",(Y132-AB132)/J132*100)</f>
       </c>
       <c r="AA132" s="4">
         <f>IF($K132="","",M132-X132)</f>
@@ -26350,7 +26350,7 @@
         <f>IF($K133="","",L133-M133-R133-S133-T133-U133-V133-W133)</f>
       </c>
       <c r="Z133" s="4">
-        <f>IF($K133="","",(Y133-AB133)/K133*100)</f>
+        <f>IF($K133="","",(Y133-AB133)/J133*100)</f>
       </c>
       <c r="AA133" s="4">
         <f>IF($K133="","",M133-X133)</f>
@@ -26401,7 +26401,7 @@
         <f>IF($K134="","",L134-M134-R134-S134-T134-U134-V134-W134)</f>
       </c>
       <c r="Z134" s="4">
-        <f>IF($K134="","",(Y134-AB134)/K134*100)</f>
+        <f>IF($K134="","",(Y134-AB134)/J134*100)</f>
       </c>
       <c r="AA134" s="4">
         <f>IF($K134="","",M134-X134)</f>
@@ -26452,7 +26452,7 @@
         <f>IF($K135="","",L135-M135-R135-S135-T135-U135-V135-W135)</f>
       </c>
       <c r="Z135" s="4">
-        <f>IF($K135="","",(Y135-AB135)/K135*100)</f>
+        <f>IF($K135="","",(Y135-AB135)/J135*100)</f>
       </c>
       <c r="AA135" s="4">
         <f>IF($K135="","",M135-X135)</f>
@@ -26503,7 +26503,7 @@
         <f>IF($K136="","",L136-M136-R136-S136-T136-U136-V136-W136)</f>
       </c>
       <c r="Z136" s="4">
-        <f>IF($K136="","",(Y136-AB136)/K136*100)</f>
+        <f>IF($K136="","",(Y136-AB136)/J136*100)</f>
       </c>
       <c r="AA136" s="4">
         <f>IF($K136="","",M136-X136)</f>
@@ -26554,7 +26554,7 @@
         <f>IF($K137="","",L137-M137-R137-S137-T137-U137-V137-W137)</f>
       </c>
       <c r="Z137" s="4">
-        <f>IF($K137="","",(Y137-AB137)/K137*100)</f>
+        <f>IF($K137="","",(Y137-AB137)/J137*100)</f>
       </c>
       <c r="AA137" s="4">
         <f>IF($K137="","",M137-X137)</f>
@@ -26605,7 +26605,7 @@
         <f>IF($K138="","",L138-M138-R138-S138-T138-U138-V138-W138)</f>
       </c>
       <c r="Z138" s="4">
-        <f>IF($K138="","",(Y138-AB138)/K138*100)</f>
+        <f>IF($K138="","",(Y138-AB138)/J138*100)</f>
       </c>
       <c r="AA138" s="4">
         <f>IF($K138="","",M138-X138)</f>
@@ -26656,7 +26656,7 @@
         <f>IF($K139="","",L139-M139-R139-S139-T139-U139-V139-W139)</f>
       </c>
       <c r="Z139" s="4">
-        <f>IF($K139="","",(Y139-AB139)/K139*100)</f>
+        <f>IF($K139="","",(Y139-AB139)/J139*100)</f>
       </c>
       <c r="AA139" s="4">
         <f>IF($K139="","",M139-X139)</f>
@@ -26707,7 +26707,7 @@
         <f>IF($K140="","",L140-M140-R140-S140-T140-U140-V140-W140)</f>
       </c>
       <c r="Z140" s="4">
-        <f>IF($K140="","",(Y140-AB140)/K140*100)</f>
+        <f>IF($K140="","",(Y140-AB140)/J140*100)</f>
       </c>
       <c r="AA140" s="4">
         <f>IF($K140="","",M140-X140)</f>
@@ -26758,7 +26758,7 @@
         <f>IF($K141="","",L141-M141-R141-S141-T141-U141-V141-W141)</f>
       </c>
       <c r="Z141" s="4">
-        <f>IF($K141="","",(Y141-AB141)/K141*100)</f>
+        <f>IF($K141="","",(Y141-AB141)/J141*100)</f>
       </c>
       <c r="AA141" s="4">
         <f>IF($K141="","",M141-X141)</f>
@@ -26809,7 +26809,7 @@
         <f>IF($K142="","",L142-M142-R142-S142-T142-U142-V142-W142)</f>
       </c>
       <c r="Z142" s="4">
-        <f>IF($K142="","",(Y142-AB142)/K142*100)</f>
+        <f>IF($K142="","",(Y142-AB142)/J142*100)</f>
       </c>
       <c r="AA142" s="4">
         <f>IF($K142="","",M142-X142)</f>
@@ -26860,7 +26860,7 @@
         <f>IF($K143="","",L143-M143-R143-S143-T143-U143-V143-W143)</f>
       </c>
       <c r="Z143" s="4">
-        <f>IF($K143="","",(Y143-AB143)/K143*100)</f>
+        <f>IF($K143="","",(Y143-AB143)/J143*100)</f>
       </c>
       <c r="AA143" s="4">
         <f>IF($K143="","",M143-X143)</f>
@@ -26911,7 +26911,7 @@
         <f>IF($K144="","",L144-M144-R144-S144-T144-U144-V144-W144)</f>
       </c>
       <c r="Z144" s="4">
-        <f>IF($K144="","",(Y144-AB144)/K144*100)</f>
+        <f>IF($K144="","",(Y144-AB144)/J144*100)</f>
       </c>
       <c r="AA144" s="4">
         <f>IF($K144="","",M144-X144)</f>
@@ -26962,7 +26962,7 @@
         <f>IF($K145="","",L145-M145-R145-S145-T145-U145-V145-W145)</f>
       </c>
       <c r="Z145" s="4">
-        <f>IF($K145="","",(Y145-AB145)/K145*100)</f>
+        <f>IF($K145="","",(Y145-AB145)/J145*100)</f>
       </c>
       <c r="AA145" s="4">
         <f>IF($K145="","",M145-X145)</f>
@@ -27013,7 +27013,7 @@
         <f>IF($K146="","",L146-M146-R146-S146-T146-U146-V146-W146)</f>
       </c>
       <c r="Z146" s="4">
-        <f>IF($K146="","",(Y146-AB146)/K146*100)</f>
+        <f>IF($K146="","",(Y146-AB146)/J146*100)</f>
       </c>
       <c r="AA146" s="4">
         <f>IF($K146="","",M146-X146)</f>
@@ -27064,7 +27064,7 @@
         <f>IF($K147="","",L147-M147-R147-S147-T147-U147-V147-W147)</f>
       </c>
       <c r="Z147" s="4">
-        <f>IF($K147="","",(Y147-AB147)/K147*100)</f>
+        <f>IF($K147="","",(Y147-AB147)/J147*100)</f>
       </c>
       <c r="AA147" s="4">
         <f>IF($K147="","",M147-X147)</f>
@@ -27115,7 +27115,7 @@
         <f>IF($K148="","",L148-M148-R148-S148-T148-U148-V148-W148)</f>
       </c>
       <c r="Z148" s="4">
-        <f>IF($K148="","",(Y148-AB148)/K148*100)</f>
+        <f>IF($K148="","",(Y148-AB148)/J148*100)</f>
       </c>
       <c r="AA148" s="4">
         <f>IF($K148="","",M148-X148)</f>
@@ -27166,7 +27166,7 @@
         <f>IF($K149="","",L149-M149-R149-S149-T149-U149-V149-W149)</f>
       </c>
       <c r="Z149" s="4">
-        <f>IF($K149="","",(Y149-AB149)/K149*100)</f>
+        <f>IF($K149="","",(Y149-AB149)/J149*100)</f>
       </c>
       <c r="AA149" s="4">
         <f>IF($K149="","",M149-X149)</f>
@@ -27217,7 +27217,7 @@
         <f>IF($K150="","",L150-M150-R150-S150-T150-U150-V150-W150)</f>
       </c>
       <c r="Z150" s="4">
-        <f>IF($K150="","",(Y150-AB150)/K150*100)</f>
+        <f>IF($K150="","",(Y150-AB150)/J150*100)</f>
       </c>
       <c r="AA150" s="4">
         <f>IF($K150="","",M150-X150)</f>
@@ -27268,7 +27268,7 @@
         <f>IF($K151="","",L151-M151-R151-S151-T151-U151-V151-W151)</f>
       </c>
       <c r="Z151" s="4">
-        <f>IF($K151="","",(Y151-AB151)/K151*100)</f>
+        <f>IF($K151="","",(Y151-AB151)/J151*100)</f>
       </c>
       <c r="AA151" s="4">
         <f>IF($K151="","",M151-X151)</f>
@@ -27319,7 +27319,7 @@
         <f>IF($K152="","",L152-M152-R152-S152-T152-U152-V152-W152)</f>
       </c>
       <c r="Z152" s="4">
-        <f>IF($K152="","",(Y152-AB152)/K152*100)</f>
+        <f>IF($K152="","",(Y152-AB152)/J152*100)</f>
       </c>
       <c r="AA152" s="4">
         <f>IF($K152="","",M152-X152)</f>
@@ -27370,7 +27370,7 @@
         <f>IF($K153="","",L153-M153-R153-S153-T153-U153-V153-W153)</f>
       </c>
       <c r="Z153" s="4">
-        <f>IF($K153="","",(Y153-AB153)/K153*100)</f>
+        <f>IF($K153="","",(Y153-AB153)/J153*100)</f>
       </c>
       <c r="AA153" s="4">
         <f>IF($K153="","",M153-X153)</f>
@@ -27421,7 +27421,7 @@
         <f>IF($K154="","",L154-M154-R154-S154-T154-U154-V154-W154)</f>
       </c>
       <c r="Z154" s="4">
-        <f>IF($K154="","",(Y154-AB154)/K154*100)</f>
+        <f>IF($K154="","",(Y154-AB154)/J154*100)</f>
       </c>
       <c r="AA154" s="4">
         <f>IF($K154="","",M154-X154)</f>
@@ -27472,7 +27472,7 @@
         <f>IF($K155="","",L155-M155-R155-S155-T155-U155-V155-W155)</f>
       </c>
       <c r="Z155" s="4">
-        <f>IF($K155="","",(Y155-AB155)/K155*100)</f>
+        <f>IF($K155="","",(Y155-AB155)/J155*100)</f>
       </c>
       <c r="AA155" s="4">
         <f>IF($K155="","",M155-X155)</f>
@@ -27523,7 +27523,7 @@
         <f>IF($K156="","",L156-M156-R156-S156-T156-U156-V156-W156)</f>
       </c>
       <c r="Z156" s="4">
-        <f>IF($K156="","",(Y156-AB156)/K156*100)</f>
+        <f>IF($K156="","",(Y156-AB156)/J156*100)</f>
       </c>
       <c r="AA156" s="4">
         <f>IF($K156="","",M156-X156)</f>
@@ -27574,7 +27574,7 @@
         <f>IF($K157="","",L157-M157-R157-S157-T157-U157-V157-W157)</f>
       </c>
       <c r="Z157" s="4">
-        <f>IF($K157="","",(Y157-AB157)/K157*100)</f>
+        <f>IF($K157="","",(Y157-AB157)/J157*100)</f>
       </c>
       <c r="AA157" s="4">
         <f>IF($K157="","",M157-X157)</f>
@@ -27625,7 +27625,7 @@
         <f>IF($K158="","",L158-M158-R158-S158-T158-U158-V158-W158)</f>
       </c>
       <c r="Z158" s="4">
-        <f>IF($K158="","",(Y158-AB158)/K158*100)</f>
+        <f>IF($K158="","",(Y158-AB158)/J158*100)</f>
       </c>
       <c r="AA158" s="4">
         <f>IF($K158="","",M158-X158)</f>
@@ -27676,7 +27676,7 @@
         <f>IF($K159="","",L159-M159-R159-S159-T159-U159-V159-W159)</f>
       </c>
       <c r="Z159" s="4">
-        <f>IF($K159="","",(Y159-AB159)/K159*100)</f>
+        <f>IF($K159="","",(Y159-AB159)/J159*100)</f>
       </c>
       <c r="AA159" s="4">
         <f>IF($K159="","",M159-X159)</f>
@@ -27727,7 +27727,7 @@
         <f>IF($K160="","",L160-M160-R160-S160-T160-U160-V160-W160)</f>
       </c>
       <c r="Z160" s="4">
-        <f>IF($K160="","",(Y160-AB160)/K160*100)</f>
+        <f>IF($K160="","",(Y160-AB160)/J160*100)</f>
       </c>
       <c r="AA160" s="4">
         <f>IF($K160="","",M160-X160)</f>
@@ -27778,7 +27778,7 @@
         <f>IF($K161="","",L161-M161-R161-S161-T161-U161-V161-W161)</f>
       </c>
       <c r="Z161" s="4">
-        <f>IF($K161="","",(Y161-AB161)/K161*100)</f>
+        <f>IF($K161="","",(Y161-AB161)/J161*100)</f>
       </c>
       <c r="AA161" s="4">
         <f>IF($K161="","",M161-X161)</f>
@@ -27829,7 +27829,7 @@
         <f>IF($K162="","",L162-M162-R162-S162-T162-U162-V162-W162)</f>
       </c>
       <c r="Z162" s="4">
-        <f>IF($K162="","",(Y162-AB162)/K162*100)</f>
+        <f>IF($K162="","",(Y162-AB162)/J162*100)</f>
       </c>
       <c r="AA162" s="4">
         <f>IF($K162="","",M162-X162)</f>
@@ -27880,7 +27880,7 @@
         <f>IF($K163="","",L163-M163-R163-S163-T163-U163-V163-W163)</f>
       </c>
       <c r="Z163" s="4">
-        <f>IF($K163="","",(Y163-AB163)/K163*100)</f>
+        <f>IF($K163="","",(Y163-AB163)/J163*100)</f>
       </c>
       <c r="AA163" s="4">
         <f>IF($K163="","",M163-X163)</f>
@@ -27931,7 +27931,7 @@
         <f>IF($K164="","",L164-M164-R164-S164-T164-U164-V164-W164)</f>
       </c>
       <c r="Z164" s="4">
-        <f>IF($K164="","",(Y164-AB164)/K164*100)</f>
+        <f>IF($K164="","",(Y164-AB164)/J164*100)</f>
       </c>
       <c r="AA164" s="4">
         <f>IF($K164="","",M164-X164)</f>
@@ -27982,7 +27982,7 @@
         <f>IF($K165="","",L165-M165-R165-S165-T165-U165-V165-W165)</f>
       </c>
       <c r="Z165" s="4">
-        <f>IF($K165="","",(Y165-AB165)/K165*100)</f>
+        <f>IF($K165="","",(Y165-AB165)/J165*100)</f>
       </c>
       <c r="AA165" s="4">
         <f>IF($K165="","",M165-X165)</f>
@@ -28033,7 +28033,7 @@
         <f>IF($K166="","",L166-M166-R166-S166-T166-U166-V166-W166)</f>
       </c>
       <c r="Z166" s="4">
-        <f>IF($K166="","",(Y166-AB166)/K166*100)</f>
+        <f>IF($K166="","",(Y166-AB166)/J166*100)</f>
       </c>
       <c r="AA166" s="4">
         <f>IF($K166="","",M166-X166)</f>
@@ -28084,7 +28084,7 @@
         <f>IF($K167="","",L167-M167-R167-S167-T167-U167-V167-W167)</f>
       </c>
       <c r="Z167" s="4">
-        <f>IF($K167="","",(Y167-AB167)/K167*100)</f>
+        <f>IF($K167="","",(Y167-AB167)/J167*100)</f>
       </c>
       <c r="AA167" s="4">
         <f>IF($K167="","",M167-X167)</f>
@@ -28135,7 +28135,7 @@
         <f>IF($K168="","",L168-M168-R168-S168-T168-U168-V168-W168)</f>
       </c>
       <c r="Z168" s="4">
-        <f>IF($K168="","",(Y168-AB168)/K168*100)</f>
+        <f>IF($K168="","",(Y168-AB168)/J168*100)</f>
       </c>
       <c r="AA168" s="4">
         <f>IF($K168="","",M168-X168)</f>
@@ -28186,7 +28186,7 @@
         <f>IF($K169="","",L169-M169-R169-S169-T169-U169-V169-W169)</f>
       </c>
       <c r="Z169" s="4">
-        <f>IF($K169="","",(Y169-AB169)/K169*100)</f>
+        <f>IF($K169="","",(Y169-AB169)/J169*100)</f>
       </c>
       <c r="AA169" s="4">
         <f>IF($K169="","",M169-X169)</f>
@@ -28237,7 +28237,7 @@
         <f>IF($K170="","",L170-M170-R170-S170-T170-U170-V170-W170)</f>
       </c>
       <c r="Z170" s="4">
-        <f>IF($K170="","",(Y170-AB170)/K170*100)</f>
+        <f>IF($K170="","",(Y170-AB170)/J170*100)</f>
       </c>
       <c r="AA170" s="4">
         <f>IF($K170="","",M170-X170)</f>
@@ -28288,7 +28288,7 @@
         <f>IF($K171="","",L171-M171-R171-S171-T171-U171-V171-W171)</f>
       </c>
       <c r="Z171" s="4">
-        <f>IF($K171="","",(Y171-AB171)/K171*100)</f>
+        <f>IF($K171="","",(Y171-AB171)/J171*100)</f>
       </c>
       <c r="AA171" s="4">
         <f>IF($K171="","",M171-X171)</f>
@@ -28339,7 +28339,7 @@
         <f>IF($K172="","",L172-M172-R172-S172-T172-U172-V172-W172)</f>
       </c>
       <c r="Z172" s="4">
-        <f>IF($K172="","",(Y172-AB172)/K172*100)</f>
+        <f>IF($K172="","",(Y172-AB172)/J172*100)</f>
       </c>
       <c r="AA172" s="4">
         <f>IF($K172="","",M172-X172)</f>
@@ -28390,7 +28390,7 @@
         <f>IF($K173="","",L173-M173-R173-S173-T173-U173-V173-W173)</f>
       </c>
       <c r="Z173" s="4">
-        <f>IF($K173="","",(Y173-AB173)/K173*100)</f>
+        <f>IF($K173="","",(Y173-AB173)/J173*100)</f>
       </c>
       <c r="AA173" s="4">
         <f>IF($K173="","",M173-X173)</f>
@@ -28441,7 +28441,7 @@
         <f>IF($K174="","",L174-M174-R174-S174-T174-U174-V174-W174)</f>
       </c>
       <c r="Z174" s="4">
-        <f>IF($K174="","",(Y174-AB174)/K174*100)</f>
+        <f>IF($K174="","",(Y174-AB174)/J174*100)</f>
       </c>
       <c r="AA174" s="4">
         <f>IF($K174="","",M174-X174)</f>
@@ -28492,7 +28492,7 @@
         <f>IF($K175="","",L175-M175-R175-S175-T175-U175-V175-W175)</f>
       </c>
       <c r="Z175" s="4">
-        <f>IF($K175="","",(Y175-AB175)/K175*100)</f>
+        <f>IF($K175="","",(Y175-AB175)/J175*100)</f>
       </c>
       <c r="AA175" s="4">
         <f>IF($K175="","",M175-X175)</f>
@@ -28543,7 +28543,7 @@
         <f>IF($K176="","",L176-M176-R176-S176-T176-U176-V176-W176)</f>
       </c>
       <c r="Z176" s="4">
-        <f>IF($K176="","",(Y176-AB176)/K176*100)</f>
+        <f>IF($K176="","",(Y176-AB176)/J176*100)</f>
       </c>
       <c r="AA176" s="4">
         <f>IF($K176="","",M176-X176)</f>
@@ -28594,7 +28594,7 @@
         <f>IF($K177="","",L177-M177-R177-S177-T177-U177-V177-W177)</f>
       </c>
       <c r="Z177" s="4">
-        <f>IF($K177="","",(Y177-AB177)/K177*100)</f>
+        <f>IF($K177="","",(Y177-AB177)/J177*100)</f>
       </c>
       <c r="AA177" s="4">
         <f>IF($K177="","",M177-X177)</f>
@@ -28645,7 +28645,7 @@
         <f>IF($K178="","",L178-M178-R178-S178-T178-U178-V178-W178)</f>
       </c>
       <c r="Z178" s="4">
-        <f>IF($K178="","",(Y178-AB178)/K178*100)</f>
+        <f>IF($K178="","",(Y178-AB178)/J178*100)</f>
       </c>
       <c r="AA178" s="4">
         <f>IF($K178="","",M178-X178)</f>
@@ -28696,7 +28696,7 @@
         <f>IF($K179="","",L179-M179-R179-S179-T179-U179-V179-W179)</f>
       </c>
       <c r="Z179" s="4">
-        <f>IF($K179="","",(Y179-AB179)/K179*100)</f>
+        <f>IF($K179="","",(Y179-AB179)/J179*100)</f>
       </c>
       <c r="AA179" s="4">
         <f>IF($K179="","",M179-X179)</f>
@@ -28747,7 +28747,7 @@
         <f>IF($K180="","",L180-M180-R180-S180-T180-U180-V180-W180)</f>
       </c>
       <c r="Z180" s="4">
-        <f>IF($K180="","",(Y180-AB180)/K180*100)</f>
+        <f>IF($K180="","",(Y180-AB180)/J180*100)</f>
       </c>
       <c r="AA180" s="4">
         <f>IF($K180="","",M180-X180)</f>
@@ -28798,7 +28798,7 @@
         <f>IF($K181="","",L181-M181-R181-S181-T181-U181-V181-W181)</f>
       </c>
       <c r="Z181" s="4">
-        <f>IF($K181="","",(Y181-AB181)/K181*100)</f>
+        <f>IF($K181="","",(Y181-AB181)/J181*100)</f>
       </c>
       <c r="AA181" s="4">
         <f>IF($K181="","",M181-X181)</f>
@@ -28849,7 +28849,7 @@
         <f>IF($K182="","",L182-M182-R182-S182-T182-U182-V182-W182)</f>
       </c>
       <c r="Z182" s="4">
-        <f>IF($K182="","",(Y182-AB182)/K182*100)</f>
+        <f>IF($K182="","",(Y182-AB182)/J182*100)</f>
       </c>
       <c r="AA182" s="4">
         <f>IF($K182="","",M182-X182)</f>
@@ -28900,7 +28900,7 @@
         <f>IF($K183="","",L183-M183-R183-S183-T183-U183-V183-W183)</f>
       </c>
       <c r="Z183" s="4">
-        <f>IF($K183="","",(Y183-AB183)/K183*100)</f>
+        <f>IF($K183="","",(Y183-AB183)/J183*100)</f>
       </c>
       <c r="AA183" s="4">
         <f>IF($K183="","",M183-X183)</f>
@@ -28951,7 +28951,7 @@
         <f>IF($K184="","",L184-M184-R184-S184-T184-U184-V184-W184)</f>
       </c>
       <c r="Z184" s="4">
-        <f>IF($K184="","",(Y184-AB184)/K184*100)</f>
+        <f>IF($K184="","",(Y184-AB184)/J184*100)</f>
       </c>
       <c r="AA184" s="4">
         <f>IF($K184="","",M184-X184)</f>
@@ -29002,7 +29002,7 @@
         <f>IF($K185="","",L185-M185-R185-S185-T185-U185-V185-W185)</f>
       </c>
       <c r="Z185" s="4">
-        <f>IF($K185="","",(Y185-AB185)/K185*100)</f>
+        <f>IF($K185="","",(Y185-AB185)/J185*100)</f>
       </c>
       <c r="AA185" s="4">
         <f>IF($K185="","",M185-X185)</f>
@@ -29053,7 +29053,7 @@
         <f>IF($K186="","",L186-M186-R186-S186-T186-U186-V186-W186)</f>
       </c>
       <c r="Z186" s="4">
-        <f>IF($K186="","",(Y186-AB186)/K186*100)</f>
+        <f>IF($K186="","",(Y186-AB186)/J186*100)</f>
       </c>
       <c r="AA186" s="4">
         <f>IF($K186="","",M186-X186)</f>
@@ -29104,7 +29104,7 @@
         <f>IF($K187="","",L187-M187-R187-S187-T187-U187-V187-W187)</f>
       </c>
       <c r="Z187" s="4">
-        <f>IF($K187="","",(Y187-AB187)/K187*100)</f>
+        <f>IF($K187="","",(Y187-AB187)/J187*100)</f>
       </c>
       <c r="AA187" s="4">
         <f>IF($K187="","",M187-X187)</f>
@@ -29155,7 +29155,7 @@
         <f>IF($K188="","",L188-M188-R188-S188-T188-U188-V188-W188)</f>
       </c>
       <c r="Z188" s="4">
-        <f>IF($K188="","",(Y188-AB188)/K188*100)</f>
+        <f>IF($K188="","",(Y188-AB188)/J188*100)</f>
       </c>
       <c r="AA188" s="4">
         <f>IF($K188="","",M188-X188)</f>
@@ -29206,7 +29206,7 @@
         <f>IF($K189="","",L189-M189-R189-S189-T189-U189-V189-W189)</f>
       </c>
       <c r="Z189" s="4">
-        <f>IF($K189="","",(Y189-AB189)/K189*100)</f>
+        <f>IF($K189="","",(Y189-AB189)/J189*100)</f>
       </c>
       <c r="AA189" s="4">
         <f>IF($K189="","",M189-X189)</f>
@@ -29257,7 +29257,7 @@
         <f>IF($K190="","",L190-M190-R190-S190-T190-U190-V190-W190)</f>
       </c>
       <c r="Z190" s="4">
-        <f>IF($K190="","",(Y190-AB190)/K190*100)</f>
+        <f>IF($K190="","",(Y190-AB190)/J190*100)</f>
       </c>
       <c r="AA190" s="4">
         <f>IF($K190="","",M190-X190)</f>
@@ -29308,7 +29308,7 @@
         <f>IF($K191="","",L191-M191-R191-S191-T191-U191-V191-W191)</f>
       </c>
       <c r="Z191" s="4">
-        <f>IF($K191="","",(Y191-AB191)/K191*100)</f>
+        <f>IF($K191="","",(Y191-AB191)/J191*100)</f>
       </c>
       <c r="AA191" s="4">
         <f>IF($K191="","",M191-X191)</f>
@@ -29359,7 +29359,7 @@
         <f>IF($K192="","",L192-M192-R192-S192-T192-U192-V192-W192)</f>
       </c>
       <c r="Z192" s="4">
-        <f>IF($K192="","",(Y192-AB192)/K192*100)</f>
+        <f>IF($K192="","",(Y192-AB192)/J192*100)</f>
       </c>
       <c r="AA192" s="4">
         <f>IF($K192="","",M192-X192)</f>
@@ -29410,7 +29410,7 @@
         <f>IF($K193="","",L193-M193-R193-S193-T193-U193-V193-W193)</f>
       </c>
       <c r="Z193" s="4">
-        <f>IF($K193="","",(Y193-AB193)/K193*100)</f>
+        <f>IF($K193="","",(Y193-AB193)/J193*100)</f>
       </c>
       <c r="AA193" s="4">
         <f>IF($K193="","",M193-X193)</f>
@@ -29461,7 +29461,7 @@
         <f>IF($K194="","",L194-M194-R194-S194-T194-U194-V194-W194)</f>
       </c>
       <c r="Z194" s="4">
-        <f>IF($K194="","",(Y194-AB194)/K194*100)</f>
+        <f>IF($K194="","",(Y194-AB194)/J194*100)</f>
       </c>
       <c r="AA194" s="4">
         <f>IF($K194="","",M194-X194)</f>
@@ -29512,7 +29512,7 @@
         <f>IF($K195="","",L195-M195-R195-S195-T195-U195-V195-W195)</f>
       </c>
       <c r="Z195" s="4">
-        <f>IF($K195="","",(Y195-AB195)/K195*100)</f>
+        <f>IF($K195="","",(Y195-AB195)/J195*100)</f>
       </c>
       <c r="AA195" s="4">
         <f>IF($K195="","",M195-X195)</f>
@@ -29563,7 +29563,7 @@
         <f>IF($K196="","",L196-M196-R196-S196-T196-U196-V196-W196)</f>
       </c>
       <c r="Z196" s="4">
-        <f>IF($K196="","",(Y196-AB196)/K196*100)</f>
+        <f>IF($K196="","",(Y196-AB196)/J196*100)</f>
       </c>
       <c r="AA196" s="4">
         <f>IF($K196="","",M196-X196)</f>
@@ -29614,7 +29614,7 @@
         <f>IF($K197="","",L197-M197-R197-S197-T197-U197-V197-W197)</f>
       </c>
       <c r="Z197" s="4">
-        <f>IF($K197="","",(Y197-AB197)/K197*100)</f>
+        <f>IF($K197="","",(Y197-AB197)/J197*100)</f>
       </c>
       <c r="AA197" s="4">
         <f>IF($K197="","",M197-X197)</f>
@@ -29665,7 +29665,7 @@
         <f>IF($K198="","",L198-M198-R198-S198-T198-U198-V198-W198)</f>
       </c>
       <c r="Z198" s="4">
-        <f>IF($K198="","",(Y198-AB198)/K198*100)</f>
+        <f>IF($K198="","",(Y198-AB198)/J198*100)</f>
       </c>
       <c r="AA198" s="4">
         <f>IF($K198="","",M198-X198)</f>
@@ -29716,7 +29716,7 @@
         <f>IF($K199="","",L199-M199-R199-S199-T199-U199-V199-W199)</f>
       </c>
       <c r="Z199" s="4">
-        <f>IF($K199="","",(Y199-AB199)/K199*100)</f>
+        <f>IF($K199="","",(Y199-AB199)/J199*100)</f>
       </c>
       <c r="AA199" s="4">
         <f>IF($K199="","",M199-X199)</f>
@@ -29767,7 +29767,7 @@
         <f>IF($K200="","",L200-M200-R200-S200-T200-U200-V200-W200)</f>
       </c>
       <c r="Z200" s="4">
-        <f>IF($K200="","",(Y200-AB200)/K200*100)</f>
+        <f>IF($K200="","",(Y200-AB200)/J200*100)</f>
       </c>
       <c r="AA200" s="4">
         <f>IF($K200="","",M200-X200)</f>
@@ -29818,7 +29818,7 @@
         <f>IF($K201="","",L201-M201-R201-S201-T201-U201-V201-W201)</f>
       </c>
       <c r="Z201" s="4">
-        <f>IF($K201="","",(Y201-AB201)/K201*100)</f>
+        <f>IF($K201="","",(Y201-AB201)/J201*100)</f>
       </c>
       <c r="AA201" s="4">
         <f>IF($K201="","",M201-X201)</f>
@@ -29869,7 +29869,7 @@
         <f>IF($K202="","",L202-M202-R202-S202-T202-U202-V202-W202)</f>
       </c>
       <c r="Z202" s="4">
-        <f>IF($K202="","",(Y202-AB202)/K202*100)</f>
+        <f>IF($K202="","",(Y202-AB202)/J202*100)</f>
       </c>
       <c r="AA202" s="4">
         <f>IF($K202="","",M202-X202)</f>
@@ -29920,7 +29920,7 @@
         <f>IF($K203="","",L203-M203-R203-S203-T203-U203-V203-W203)</f>
       </c>
       <c r="Z203" s="4">
-        <f>IF($K203="","",(Y203-AB203)/K203*100)</f>
+        <f>IF($K203="","",(Y203-AB203)/J203*100)</f>
       </c>
       <c r="AA203" s="4">
         <f>IF($K203="","",M203-X203)</f>
@@ -29971,7 +29971,7 @@
         <f>IF($K204="","",L204-M204-R204-S204-T204-U204-V204-W204)</f>
       </c>
       <c r="Z204" s="4">
-        <f>IF($K204="","",(Y204-AB204)/K204*100)</f>
+        <f>IF($K204="","",(Y204-AB204)/J204*100)</f>
       </c>
       <c r="AA204" s="4">
         <f>IF($K204="","",M204-X204)</f>
@@ -46461,7 +46461,7 @@
         <v>7.83</v>
       </c>
       <c r="K3" s="18">
-        <v>43.57</v>
+        <v>237.27</v>
       </c>
       <c r="L3" t="s">
         <v>1</v>
